--- a/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26205" windowHeight="7740"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,104 +31,285 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
-    <t>对账单号</t>
-  </si>
-  <si>
-    <t>单据状态</t>
-  </si>
-  <si>
-    <t>对账周期</t>
-  </si>
-  <si>
-    <t>物流商</t>
-  </si>
-  <si>
-    <t>费用合计</t>
-  </si>
-  <si>
-    <t>实际物流运费</t>
-  </si>
-  <si>
-    <t>实际报关费用</t>
-  </si>
-  <si>
-    <t>实际其他费用</t>
-  </si>
-  <si>
-    <t>实际计费重量</t>
-  </si>
-  <si>
-    <t>结算币种</t>
-  </si>
-  <si>
-    <t>生成对账日期</t>
-  </si>
-  <si>
-    <t>提交对账日期</t>
-  </si>
-  <si>
-    <t>审核对账日期</t>
-  </si>
-  <si>
-    <t>最新不通过原因</t>
-  </si>
-  <si>
-    <t>{.code}</t>
-  </si>
-  <si>
-    <t>{.approveStatusName}</t>
-  </si>
-  <si>
-    <t>{.cycle}</t>
-  </si>
-  <si>
-    <t>{.logisticsSupplierName}</t>
-  </si>
-  <si>
-    <t>{.totalCost}</t>
-  </si>
-  <si>
-    <t>{.actualShippingCost}</t>
-  </si>
-  <si>
-    <t>{.actualDeclareCost}</t>
-  </si>
-  <si>
-    <t>{.actualOtherCost}</t>
-  </si>
-  <si>
-    <t>{.actualBillingWeight}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>发货单号</t>
+    </r>
+  </si>
+  <si>
+    <t>业务单号</t>
+  </si>
+  <si>
+    <t>店铺</t>
+  </si>
+  <si>
+    <t>仓库</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SKU</t>
+    </r>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>初始签收数量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>期初在途头程费用</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>期初在途头程关税</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>期初暂估头程费用</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>期初暂估头程关税</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>分摊重量(KG)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品成本</t>
+    </r>
+  </si>
+  <si>
+    <t>币种（默认CNY）</t>
+  </si>
+  <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.businessCode}</t>
+  </si>
+  <si>
+    <t>{.shopName}</t>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.initReceiveQty}</t>
+  </si>
+  <si>
+    <t>{.initTransitCost}</t>
+  </si>
+  <si>
+    <t>{.initTransitTariff}</t>
+  </si>
+  <si>
+    <t>{.initEstimatedCost}</t>
+  </si>
+  <si>
+    <t>{.initEstimatedTariff}</t>
+  </si>
+  <si>
+    <t>{.weightAllocation}</t>
+  </si>
+  <si>
+    <t>{.productCost}</t>
   </si>
   <si>
     <t>{.currency}</t>
-  </si>
-  <si>
-    <t>{.reconciliationDate}</t>
-  </si>
-  <si>
-    <t>{.submitDate}</t>
-  </si>
-  <si>
-    <t>{.approveDate}</t>
-  </si>
-  <si>
-    <t>{.reason}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.000000_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -598,138 +779,159 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1063,7 +1265,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1075,31 +1277,31 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
@@ -1125,25 +1327,25 @@
       <c r="F2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="7" t="s">
         <v>26</v>
       </c>
       <c r="N2" t="s">

--- a/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationExport.xlsx
@@ -296,7 +296,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.0000_ "/>
     <numFmt numFmtId="178" formatCode="0.000000_ "/>
   </numFmts>
   <fonts count="21">
@@ -913,6 +913,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -922,16 +931,7 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1254,18 +1254,18 @@
     <col min="4" max="4" width="21.625" customWidth="1"/>
     <col min="5" max="5" width="18.875" customWidth="1"/>
     <col min="6" max="6" width="24.125" customWidth="1"/>
-    <col min="7" max="7" width="21.75" customWidth="1"/>
-    <col min="8" max="8" width="20.375" customWidth="1"/>
-    <col min="9" max="9" width="19.375" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
-    <col min="11" max="11" width="23.75" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="17.375" customWidth="1"/>
+    <col min="7" max="7" width="21.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="23.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.375" style="3" customWidth="1"/>
     <col min="14" max="14" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1277,31 +1277,31 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
@@ -1327,25 +1327,25 @@
       <c r="F2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="N2" t="s">

--- a/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationExport.xlsx
@@ -29,7 +29,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>期初单号</t>
+  </si>
+  <si>
+    <t>单据状态</t>
+  </si>
   <si>
     <r>
       <rPr>
@@ -244,6 +250,18 @@
     <t>币种（默认CNY）</t>
   </si>
   <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>创建时间</t>
+  </si>
+  <si>
+    <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.statusName}</t>
+  </si>
+  <si>
     <t>{.sourceCode}</t>
   </si>
   <si>
@@ -284,6 +302,12 @@
   </si>
   <si>
     <t>{.currency}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
   </si>
 </sst>
 </file>
@@ -1245,51 +1269,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="14.375" customWidth="1"/>
-    <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="14.75" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="5" width="18.875" customWidth="1"/>
-    <col min="6" max="6" width="24.125" customWidth="1"/>
-    <col min="7" max="7" width="21.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="23.75" style="2" customWidth="1"/>
-    <col min="12" max="12" width="17" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="15.625" customWidth="1"/>
+    <col min="1" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="3" width="14.375" customWidth="1"/>
+    <col min="4" max="4" width="21.5" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="6" width="21.625" customWidth="1"/>
+    <col min="7" max="7" width="18.875" customWidth="1"/>
+    <col min="8" max="8" width="24.125" customWidth="1"/>
+    <col min="9" max="9" width="21.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15.125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="23.75" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17" style="2" customWidth="1"/>
+    <col min="15" max="15" width="17.375" style="3" customWidth="1"/>
+    <col min="16" max="18" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="6" t="s">
@@ -1301,55 +1326,79 @@
       <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationExport.xlsx
+++ b/erp-server/erp-server-tms/src/main/resources/excel/initFirstMileAllocationExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>期初单号</t>
   </si>
@@ -247,9 +247,6 @@
     </r>
   </si>
   <si>
-    <t>币种（默认CNY）</t>
-  </si>
-  <si>
     <t>创建人</t>
   </si>
   <si>
@@ -299,9 +296,6 @@
   </si>
   <si>
     <t>{.productCost}</t>
-  </si>
-  <si>
-    <t>{.currency}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1269,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="15.125" customWidth="1"/>
@@ -1286,10 +1280,10 @@
     <col min="13" max="13" width="23.75" style="2" customWidth="1"/>
     <col min="14" max="14" width="17" style="2" customWidth="1"/>
     <col min="15" max="15" width="17.375" style="3" customWidth="1"/>
-    <col min="16" max="18" width="15.625" customWidth="1"/>
+    <col min="16" max="17" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1341,64 +1335,58 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" t="s">
         <v>32</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>33</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
